--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_grid_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_grid_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>48.21</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>
